--- a/output/【河洛話注音】《水龍吟·登建康賞心亭》.xlsx
+++ b/output/【河洛話注音】《水龍吟·登建康賞心亭》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Piau-Im\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDBD63C-7287-412B-8160-8D147162A72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C766A60-9C9A-4FFB-BBA8-8F277B3AB7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21480" windowHeight="11895" firstSheet="1" activeTab="1" xr2:uid="{BF481C1B-D385-46B9-9CCA-9BADEBE96FDC}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="17280" windowHeight="12870" firstSheet="1" activeTab="1" xr2:uid="{BF481C1B-D385-46B9-9CCA-9BADEBE96FDC}"/>
   </bookViews>
   <sheets>
     <sheet name="閩拼拼音" sheetId="10" r:id="rId1"/>
@@ -1859,9 +1859,6 @@
 </t>
   </si>
   <si>
-    <t>&lt;div class='zhu_yin'&gt;&lt;p class='title'&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;水&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄙㄨㄧˋ&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -3131,6 +3128,9 @@
   </si>
   <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;淚&lt;/rb&gt;&lt;rt&gt;lui7&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄌㄨㄧ˫&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div class='Piau_Im'&gt;&lt;p class='title'&gt;</t>
   </si>
 </sst>
 </file>
@@ -7774,12 +7774,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="255">
       <c r="A1" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7789,17 +7789,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -7809,32 +7809,32 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -7854,32 +7854,32 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -7889,37 +7889,37 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -7929,22 +7929,22 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -7954,22 +7954,22 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -7979,22 +7979,22 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -8004,22 +8004,22 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -8029,22 +8029,22 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -8054,22 +8054,22 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -8079,27 +8079,27 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -8109,22 +8109,22 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -8134,17 +8134,17 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -8154,17 +8154,17 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -8179,32 +8179,32 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -8214,17 +8214,17 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="92" spans="1:1">
@@ -8234,22 +8234,22 @@
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="97" spans="1:1">
@@ -8259,22 +8259,22 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -8284,22 +8284,22 @@
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -8309,22 +8309,22 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="112" spans="1:1">
@@ -8334,22 +8334,22 @@
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="117" spans="1:1">
@@ -8359,22 +8359,22 @@
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="122" spans="1:1">
@@ -8384,22 +8384,22 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="127" spans="1:1">
@@ -8409,27 +8409,27 @@
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -8439,22 +8439,22 @@
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -8464,22 +8464,22 @@
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -8513,12 +8513,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="255">
       <c r="A1" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -8528,17 +8528,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -8548,32 +8548,32 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -8593,32 +8593,32 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -8628,37 +8628,37 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -8668,22 +8668,22 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -8693,22 +8693,22 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -8718,22 +8718,22 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -8743,22 +8743,22 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -8768,22 +8768,22 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -8793,22 +8793,22 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -8818,27 +8818,27 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -8848,22 +8848,22 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -8873,17 +8873,17 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -8893,17 +8893,17 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -8918,32 +8918,32 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -8953,17 +8953,17 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="92" spans="1:1">
@@ -8973,22 +8973,22 @@
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="97" spans="1:1">
@@ -8998,22 +8998,22 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -9023,22 +9023,22 @@
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -9048,22 +9048,22 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="112" spans="1:1">
@@ -9073,22 +9073,22 @@
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="117" spans="1:1">
@@ -9098,22 +9098,22 @@
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="122" spans="1:1">
@@ -9123,22 +9123,22 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="127" spans="1:1">
@@ -9148,27 +9148,27 @@
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -9178,22 +9178,22 @@
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -9208,17 +9208,17 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -9252,12 +9252,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="255">
       <c r="A1" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -9292,7 +9292,7 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -9302,7 +9302,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -9332,7 +9332,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -9382,7 +9382,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -9407,22 +9407,22 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -9432,12 +9432,12 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -9447,7 +9447,7 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -9462,7 +9462,7 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -9492,12 +9492,12 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -9507,7 +9507,7 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -9542,12 +9542,12 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -9557,7 +9557,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -9567,7 +9567,7 @@
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -9592,7 +9592,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -9602,7 +9602,7 @@
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -9622,7 +9622,7 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -9642,7 +9642,7 @@
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -9662,7 +9662,7 @@
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -9682,7 +9682,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -9692,7 +9692,7 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="90" spans="1:1">
@@ -9702,7 +9702,7 @@
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="92" spans="1:1">
@@ -9712,12 +9712,12 @@
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -9727,7 +9727,7 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="97" spans="1:1">
@@ -9767,7 +9767,7 @@
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="105" spans="1:1">
@@ -9797,7 +9797,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -9837,22 +9837,22 @@
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="122" spans="1:1">
@@ -9862,12 +9862,12 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="125" spans="1:1">
@@ -9877,7 +9877,7 @@
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="127" spans="1:1">
@@ -9892,7 +9892,7 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="130" spans="1:1">
@@ -9907,7 +9907,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -9947,12 +9947,12 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="142" spans="1:1">
@@ -9991,12 +9991,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="255">
       <c r="A1" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -10031,7 +10031,7 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -10041,7 +10041,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -10071,7 +10071,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -10121,7 +10121,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -10146,22 +10146,22 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -10171,12 +10171,12 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -10186,7 +10186,7 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -10201,7 +10201,7 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -10231,12 +10231,12 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -10246,7 +10246,7 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -10281,12 +10281,12 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -10296,7 +10296,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -10306,7 +10306,7 @@
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -10331,7 +10331,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -10341,7 +10341,7 @@
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -10361,7 +10361,7 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -10381,7 +10381,7 @@
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -10401,7 +10401,7 @@
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -10421,7 +10421,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -10431,7 +10431,7 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="90" spans="1:1">
@@ -10441,7 +10441,7 @@
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="92" spans="1:1">
@@ -10451,12 +10451,12 @@
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -10466,7 +10466,7 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="97" spans="1:1">
@@ -10506,7 +10506,7 @@
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="105" spans="1:1">
@@ -10536,7 +10536,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -10576,22 +10576,22 @@
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="122" spans="1:1">
@@ -10601,12 +10601,12 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="125" spans="1:1">
@@ -10616,7 +10616,7 @@
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="127" spans="1:1">
@@ -10641,12 +10641,12 @@
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -10686,12 +10686,12 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="142" spans="1:1">
@@ -10730,12 +10730,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="255">
       <c r="A1" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -10770,7 +10770,7 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -10780,7 +10780,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -10810,7 +10810,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -10860,7 +10860,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -10875,7 +10875,7 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -10885,22 +10885,22 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -10910,12 +10910,12 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -10925,7 +10925,7 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -10940,7 +10940,7 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -10970,12 +10970,12 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -10985,7 +10985,7 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -11020,12 +11020,12 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -11035,7 +11035,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -11045,7 +11045,7 @@
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -11070,7 +11070,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -11080,7 +11080,7 @@
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -11100,7 +11100,7 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -11120,7 +11120,7 @@
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -11140,7 +11140,7 @@
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -11160,7 +11160,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -11170,7 +11170,7 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="90" spans="1:1">
@@ -11180,7 +11180,7 @@
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="92" spans="1:1">
@@ -11190,12 +11190,12 @@
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -11205,7 +11205,7 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="97" spans="1:1">
@@ -11245,7 +11245,7 @@
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="105" spans="1:1">
@@ -11275,7 +11275,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -11315,22 +11315,22 @@
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="122" spans="1:1">
@@ -11340,12 +11340,12 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="125" spans="1:1">
@@ -11355,7 +11355,7 @@
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="127" spans="1:1">
@@ -11385,7 +11385,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -11425,12 +11425,12 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="142" spans="1:1">
@@ -11474,7 +11474,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>589</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -11484,17 +11484,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -11504,32 +11504,32 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -11549,32 +11549,32 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -11584,37 +11584,37 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -11624,22 +11624,22 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -11649,22 +11649,22 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -11674,22 +11674,22 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -11699,22 +11699,22 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -11724,22 +11724,22 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -11749,22 +11749,22 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -11774,27 +11774,27 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -11804,22 +11804,22 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -11829,17 +11829,17 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -11849,17 +11849,17 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -11874,32 +11874,32 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -11909,17 +11909,17 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="92" spans="1:1">
@@ -11929,22 +11929,22 @@
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="97" spans="1:1">
@@ -11954,22 +11954,22 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -11979,22 +11979,22 @@
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -12004,22 +12004,22 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="112" spans="1:1">
@@ -12029,22 +12029,22 @@
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="117" spans="1:1">
@@ -12054,22 +12054,22 @@
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="122" spans="1:1">
@@ -12079,22 +12079,22 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="127" spans="1:1">
@@ -12104,27 +12104,27 @@
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -12134,22 +12134,22 @@
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -12164,17 +12164,17 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="143" spans="1:1">
